--- a/Integration Quality/EMPRESAS/Relatorio - GRUPO KONTIK.xlsx
+++ b/Integration Quality/EMPRESAS/Relatorio - GRUPO KONTIK.xlsx
@@ -717,12 +717,12 @@
       <c r="E2" s="6" t="n">
         <v>45834.4492824074</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -906,12 +906,12 @@
       <c r="E3" s="6" t="n">
         <v>45834.45023148148</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1095,12 +1095,12 @@
       <c r="E4" s="6" t="n">
         <v>45842.51466435185</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1286,12 +1286,12 @@
       <c r="E5" s="6" t="n">
         <v>45838.97155092593</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1477,12 +1477,12 @@
       <c r="E6" s="6" t="n">
         <v>45838.97155092593</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -2804,12 +2804,12 @@
       <c r="E13" s="6" t="n">
         <v>45840.54240740741</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -2995,12 +2995,12 @@
       <c r="E14" s="6" t="n">
         <v>45840.54239583333</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -5834,12 +5834,12 @@
       <c r="E29" s="6" t="n">
         <v>45842.511875</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -6214,12 +6214,12 @@
       <c r="E31" s="6" t="n">
         <v>45842.511875</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -6596,12 +6596,12 @@
       <c r="E33" s="6" t="n">
         <v>45839.70172453704</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -7354,14 +7354,14 @@
       <c r="E37" s="6" t="n">
         <v>45842.51189814815</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -7734,12 +7734,12 @@
       <c r="E39" s="6" t="n">
         <v>45842.51188657407</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>31 dias ou +</t>
         </is>
@@ -7927,12 +7927,12 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -9628,14 +9628,14 @@
       <c r="E49" s="6" t="n">
         <v>45842.51190972222</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -10575,14 +10575,14 @@
       <c r="E54" s="6" t="n">
         <v>45831.94475694445</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -10764,14 +10764,14 @@
       <c r="E55" s="6" t="n">
         <v>45831.50702546296</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -11522,12 +11522,12 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -11898,14 +11898,14 @@
       <c r="E61" s="6" t="n">
         <v>45839.78875</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -12278,12 +12278,12 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -12465,14 +12465,14 @@
       <c r="E64" s="6" t="n">
         <v>45842.5119212963</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -12656,14 +12656,14 @@
       <c r="E65" s="6" t="n">
         <v>45842.51189814815</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -12847,14 +12847,14 @@
       <c r="E66" s="6" t="n">
         <v>45842.51527777778</v>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -13418,12 +13418,12 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -13607,12 +13607,12 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -14361,14 +14361,14 @@
       <c r="E74" s="6" t="n">
         <v>45831.93626157408</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -15119,12 +15119,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -15497,12 +15497,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -15684,14 +15684,14 @@
       <c r="E81" s="6" t="n">
         <v>45831.62175925926</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -15875,12 +15875,12 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -16064,12 +16064,12 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -16442,12 +16442,12 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -16631,12 +16631,12 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -16820,12 +16820,12 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -17009,12 +17009,12 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -17196,14 +17196,14 @@
       <c r="E89" s="6" t="n">
         <v>45839.78560185185</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -17385,14 +17385,14 @@
       <c r="E90" s="6" t="n">
         <v>45831.39997685186</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -17576,12 +17576,12 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -17765,12 +17765,12 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -17954,12 +17954,12 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -18143,12 +18143,12 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>24 a 31 dias</t>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -18330,14 +18330,14 @@
       <c r="E95" s="6" t="n">
         <v>45831.94780092593</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -18519,14 +18519,14 @@
       <c r="E96" s="6" t="n">
         <v>45835.34628472223</v>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -18710,14 +18710,14 @@
       <c r="E97" s="6" t="n">
         <v>45831.48329861111</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -18899,14 +18899,14 @@
       <c r="E98" s="6" t="n">
         <v>45831.48329861111</v>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -19088,14 +19088,14 @@
       <c r="E99" s="6" t="n">
         <v>45838.6917824074</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -19281,14 +19281,14 @@
       <c r="E100" s="6" t="n">
         <v>45835.21988425926</v>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -19474,14 +19474,14 @@
       <c r="E101" s="6" t="n">
         <v>45835.21988425926</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -19667,14 +19667,14 @@
       <c r="E102" s="6" t="n">
         <v>45832.03516203703</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -19858,14 +19858,14 @@
       <c r="E103" s="6" t="n">
         <v>45832.03863425926</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -20049,14 +20049,14 @@
       <c r="E104" s="6" t="n">
         <v>45832.93943287037</v>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -20240,14 +20240,14 @@
       <c r="E105" s="6" t="n">
         <v>45832.06626157407</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -20429,14 +20429,14 @@
       <c r="E106" s="6" t="n">
         <v>45833.79900462963</v>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -20620,14 +20620,14 @@
       <c r="E107" s="6" t="n">
         <v>45832.70055555556</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -20809,14 +20809,14 @@
       <c r="E108" s="6" t="n">
         <v>45838.64496527778</v>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -20998,14 +20998,14 @@
       <c r="E109" s="6" t="n">
         <v>45832.63414351852</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -21187,14 +21187,14 @@
       <c r="E110" s="6" t="n">
         <v>45832.63416666666</v>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -21376,14 +21376,14 @@
       <c r="E111" s="6" t="n">
         <v>45836.55931712963</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -21565,14 +21565,14 @@
       <c r="E112" s="6" t="n">
         <v>45839.23606481482</v>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -21756,14 +21756,14 @@
       <c r="E113" s="6" t="n">
         <v>45834.26790509259</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -21947,14 +21947,14 @@
       <c r="E114" s="6" t="n">
         <v>45839.36915509259</v>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -22138,14 +22138,14 @@
       <c r="E115" s="6" t="n">
         <v>45839.70216435185</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -22329,14 +22329,14 @@
       <c r="E116" s="6" t="n">
         <v>45839.70215277778</v>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -22520,14 +22520,14 @@
       <c r="E117" s="6" t="n">
         <v>45839.70212962963</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -22711,14 +22711,14 @@
       <c r="E118" s="6" t="n">
         <v>45839.37579861111</v>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -22902,14 +22902,14 @@
       <c r="E119" s="6" t="n">
         <v>45839.23611111111</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -23093,14 +23093,14 @@
       <c r="E120" s="6" t="n">
         <v>45839.24527777778</v>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -23284,14 +23284,14 @@
       <c r="E121" s="6" t="n">
         <v>45834.1674537037</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -23473,14 +23473,14 @@
       <c r="E122" s="6" t="n">
         <v>45836.56334490741</v>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -23662,14 +23662,14 @@
       <c r="E123" s="6" t="n">
         <v>45836.56336805555</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -23851,14 +23851,14 @@
       <c r="E124" s="6" t="n">
         <v>45831.74671296297</v>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -24040,14 +24040,14 @@
       <c r="E125" s="6" t="n">
         <v>45834.3234837963</v>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -24229,14 +24229,14 @@
       <c r="E126" s="6" t="n">
         <v>45833.25534722222</v>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -24420,14 +24420,14 @@
       <c r="E127" s="6" t="n">
         <v>45836.26069444444</v>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -24611,14 +24611,14 @@
       <c r="E128" s="6" t="n">
         <v>45836.26063657407</v>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -24802,14 +24802,14 @@
       <c r="E129" s="6" t="n">
         <v>45836.2606712963</v>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -24993,14 +24993,14 @@
       <c r="E130" s="6" t="n">
         <v>45837.22171296296</v>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -25184,14 +25184,14 @@
       <c r="E131" s="6" t="n">
         <v>45832.00079861111</v>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -25373,14 +25373,14 @@
       <c r="E132" s="6" t="n">
         <v>45834.94020833333</v>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -25562,14 +25562,14 @@
       <c r="E133" s="6" t="n">
         <v>45834.9525</v>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -25751,14 +25751,14 @@
       <c r="E134" s="6" t="n">
         <v>45835.70057870371</v>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -25942,14 +25942,14 @@
       <c r="E135" s="6" t="n">
         <v>45835.70060185185</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -26133,14 +26133,14 @@
       <c r="E136" s="6" t="n">
         <v>45834.32559027777</v>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -26324,14 +26324,14 @@
       <c r="E137" s="6" t="n">
         <v>45836.71452546296</v>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -26513,14 +26513,14 @@
       <c r="E138" s="6" t="n">
         <v>45842.5119675926</v>
       </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -26704,14 +26704,14 @@
       <c r="E139" s="6" t="n">
         <v>45842.51200231481</v>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -26895,14 +26895,14 @@
       <c r="E140" s="6" t="n">
         <v>45835.44207175926</v>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -27086,14 +27086,14 @@
       <c r="E141" s="6" t="n">
         <v>45831.65863425926</v>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -27277,14 +27277,14 @@
       <c r="E142" s="6" t="n">
         <v>45836.33783564815</v>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -27466,14 +27466,14 @@
       <c r="E143" s="6" t="n">
         <v>45833.9174537037</v>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -27655,14 +27655,14 @@
       <c r="E144" s="6" t="n">
         <v>45837.66371527778</v>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -27844,14 +27844,14 @@
       <c r="E145" s="6" t="n">
         <v>45837.63951388889</v>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -28033,14 +28033,14 @@
       <c r="E146" s="6" t="n">
         <v>45834.91752314815</v>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -28222,14 +28222,14 @@
       <c r="E147" s="6" t="n">
         <v>45833.95179398148</v>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -28411,14 +28411,14 @@
       <c r="E148" s="6" t="n">
         <v>45835.78684027777</v>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -28600,14 +28600,14 @@
       <c r="E149" s="6" t="n">
         <v>45831.95980324074</v>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -28789,14 +28789,14 @@
       <c r="E150" s="6" t="n">
         <v>45836.25787037037</v>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -28980,14 +28980,14 @@
       <c r="E151" s="6" t="n">
         <v>45831.95981481481</v>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -29169,14 +29169,14 @@
       <c r="E152" s="6" t="n">
         <v>45834.32344907407</v>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -29358,14 +29358,14 @@
       <c r="E153" s="6" t="n">
         <v>45834.32347222222</v>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -29547,14 +29547,14 @@
       <c r="E154" s="6" t="n">
         <v>45836.50074074074</v>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -29736,14 +29736,14 @@
       <c r="E155" s="6" t="n">
         <v>45842.51193287037</v>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -29927,14 +29927,14 @@
       <c r="E156" s="6" t="n">
         <v>45838.62333333334</v>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -30118,14 +30118,14 @@
       <c r="E157" s="6" t="n">
         <v>45835.78678240741</v>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -30307,14 +30307,14 @@
       <c r="E158" s="6" t="n">
         <v>45839.79042824074</v>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -30496,14 +30496,14 @@
       <c r="E159" s="6" t="n">
         <v>45834.78508101852</v>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -30685,14 +30685,14 @@
       <c r="E160" s="6" t="n">
         <v>45835.92758101852</v>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -30874,14 +30874,14 @@
       <c r="E161" s="6" t="n">
         <v>45834.88230324074</v>
       </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -31063,14 +31063,14 @@
       <c r="E162" s="6" t="n">
         <v>45834.93582175926</v>
       </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -31252,14 +31252,14 @@
       <c r="E163" s="6" t="n">
         <v>45834.95241898148</v>
       </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -31441,14 +31441,14 @@
       <c r="E164" s="6" t="n">
         <v>45842.56704861111</v>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -31632,14 +31632,14 @@
       <c r="E165" s="6" t="n">
         <v>45835.78856481481</v>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -31821,14 +31821,14 @@
       <c r="E166" s="6" t="n">
         <v>45833.28486111111</v>
       </c>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G166" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -32014,14 +32014,14 @@
       <c r="E167" s="6" t="n">
         <v>45839.701875</v>
       </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -32205,14 +32205,14 @@
       <c r="E168" s="6" t="n">
         <v>45833.38631944444</v>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -32394,14 +32394,14 @@
       <c r="E169" s="6" t="n">
         <v>45836.43415509259</v>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -32583,14 +32583,14 @@
       <c r="E170" s="6" t="n">
         <v>45836.963125</v>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -32774,14 +32774,14 @@
       <c r="E171" s="6" t="n">
         <v>45831.63591435185</v>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -32963,14 +32963,14 @@
       <c r="E172" s="6" t="n">
         <v>45835.93958333333</v>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -33152,14 +33152,14 @@
       <c r="E173" s="6" t="n">
         <v>45835.74180555555</v>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -33341,14 +33341,14 @@
       <c r="E174" s="6" t="n">
         <v>45842.51269675926</v>
       </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G174" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -33534,14 +33534,14 @@
       <c r="E175" s="6" t="n">
         <v>45835.77829861111</v>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -33723,14 +33723,14 @@
       <c r="E176" s="6" t="n">
         <v>45832.52119212963</v>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -33912,14 +33912,14 @@
       <c r="E177" s="6" t="n">
         <v>45835.79027777778</v>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>09 a 15 dias</t>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>31 dias ou +</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -34101,14 +34101,14 @@
       <c r="E178" s="6" t="n">
         <v>45838.93103009259</v>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -34292,14 +34292,14 @@
       <c r="E179" s="6" t="n">
         <v>45838.85490740741</v>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -34483,14 +34483,14 @@
       <c r="E180" s="6" t="n">
         <v>45838.93421296297</v>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -34674,14 +34674,14 @@
       <c r="E181" s="6" t="n">
         <v>45838.85502314815</v>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -34865,14 +34865,14 @@
       <c r="E182" s="6" t="n">
         <v>45838.93421296297</v>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -35056,14 +35056,14 @@
       <c r="E183" s="6" t="n">
         <v>45838.85511574074</v>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -35247,14 +35247,14 @@
       <c r="E184" s="6" t="n">
         <v>45842.21284722222</v>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
@@ -35440,14 +35440,14 @@
       <c r="E185" s="6" t="n">
         <v>45839.04251157407</v>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -35631,14 +35631,14 @@
       <c r="E186" s="6" t="n">
         <v>45842.8205787037</v>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -35822,14 +35822,14 @@
       <c r="E187" s="6" t="n">
         <v>45842.51270833334</v>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -36013,14 +36013,14 @@
       <c r="E188" s="6" t="n">
         <v>45839.73667824074</v>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -36204,14 +36204,14 @@
       <c r="E189" s="6" t="n">
         <v>45839.76092592593</v>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -36395,14 +36395,14 @@
       <c r="E190" s="6" t="n">
         <v>45841.54996527778</v>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -36586,14 +36586,14 @@
       <c r="E191" s="6" t="n">
         <v>45839.80307870371</v>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -36777,14 +36777,14 @@
       <c r="E192" s="6" t="n">
         <v>45841.76424768518</v>
       </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -36966,14 +36966,14 @@
       <c r="E193" s="6" t="n">
         <v>45840.40679398148</v>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -37155,14 +37155,14 @@
       <c r="E194" s="6" t="n">
         <v>45839.81730324074</v>
       </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G194" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -37344,14 +37344,14 @@
       <c r="E195" s="6" t="n">
         <v>45840.80640046296</v>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -37533,14 +37533,14 @@
       <c r="E196" s="6" t="n">
         <v>45839.65042824074</v>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
@@ -37722,14 +37722,14 @@
       <c r="E197" s="6" t="n">
         <v>45839.65042824074</v>
       </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -37911,14 +37911,14 @@
       <c r="E198" s="6" t="n">
         <v>45841.47732638889</v>
       </c>
-      <c r="F198" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G198" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -38100,14 +38100,14 @@
       <c r="E199" s="6" t="n">
         <v>45842.51210648148</v>
       </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -38291,14 +38291,14 @@
       <c r="E200" s="6" t="n">
         <v>45840.87194444444</v>
       </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -38482,14 +38482,14 @@
       <c r="E201" s="6" t="n">
         <v>45840.87194444444</v>
       </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -38671,14 +38671,14 @@
       <c r="E202" s="6" t="n">
         <v>45842.51208333333</v>
       </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -38862,14 +38862,14 @@
       <c r="E203" s="6" t="n">
         <v>45842.5120949074</v>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -39053,14 +39053,14 @@
       <c r="E204" s="6" t="n">
         <v>45842.51204861111</v>
       </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -39244,14 +39244,14 @@
       <c r="E205" s="6" t="n">
         <v>45841.6299537037</v>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -39435,14 +39435,14 @@
       <c r="E206" s="6" t="n">
         <v>45842.21232638889</v>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
@@ -39626,14 +39626,14 @@
       <c r="E207" s="6" t="n">
         <v>45840.77342592592</v>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -39817,14 +39817,14 @@
       <c r="E208" s="6" t="n">
         <v>45845.19909722222</v>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -40008,14 +40008,14 @@
       <c r="E209" s="6" t="n">
         <v>45840.23885416667</v>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -40199,14 +40199,14 @@
       <c r="E210" s="6" t="n">
         <v>45840.23988425926</v>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -40390,14 +40390,14 @@
       <c r="E211" s="6" t="n">
         <v>45841.5147337963</v>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
@@ -40579,14 +40579,14 @@
       <c r="E212" s="6" t="n">
         <v>45842.51202546297</v>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -40770,14 +40770,14 @@
       <c r="E213" s="6" t="n">
         <v>45841.23699074074</v>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -40961,14 +40961,14 @@
       <c r="E214" s="6" t="n">
         <v>45840.70916666667</v>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -41150,14 +41150,14 @@
       <c r="E215" s="6" t="n">
         <v>45841.46545138889</v>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
@@ -41339,14 +41339,14 @@
       <c r="E216" s="6" t="n">
         <v>45839.56207175926</v>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -41530,14 +41530,14 @@
       <c r="E217" s="6" t="n">
         <v>45839.36011574074</v>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -41719,14 +41719,14 @@
       <c r="E218" s="6" t="n">
         <v>45838.91421296296</v>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -41908,14 +41908,14 @@
       <c r="E219" s="6" t="n">
         <v>45839.83104166666</v>
       </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -42097,14 +42097,14 @@
       <c r="E220" s="6" t="n">
         <v>45839.81023148148</v>
       </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -42286,14 +42286,14 @@
       <c r="E221" s="6" t="n">
         <v>45840.59555555556</v>
       </c>
-      <c r="F221" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -42475,14 +42475,14 @@
       <c r="E222" s="6" t="n">
         <v>45839.88938657408</v>
       </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
-      <c r="G222" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -42664,14 +42664,14 @@
       <c r="E223" s="6" t="n">
         <v>45840.54902777778</v>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -42853,14 +42853,14 @@
       <c r="E224" s="6" t="n">
         <v>45842.93042824074</v>
       </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -43044,14 +43044,14 @@
       <c r="E225" s="6" t="n">
         <v>45843.20862268518</v>
       </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -43235,14 +43235,14 @@
       <c r="E226" s="6" t="n">
         <v>45843.21358796296</v>
       </c>
-      <c r="F226" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -43428,14 +43428,14 @@
       <c r="E227" s="6" t="n">
         <v>45843.21359953703</v>
       </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G227" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -43621,14 +43621,14 @@
       <c r="E228" s="6" t="n">
         <v>45842.72170138889</v>
       </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G228" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -43814,14 +43814,14 @@
       <c r="E229" s="6" t="n">
         <v>45842.67949074074</v>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -44007,14 +44007,14 @@
       <c r="E230" s="6" t="n">
         <v>45841.82359953703</v>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -44198,14 +44198,14 @@
       <c r="E231" s="6" t="n">
         <v>45842.56425925926</v>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -44389,14 +44389,14 @@
       <c r="E232" s="6" t="n">
         <v>45842.56427083333</v>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -44580,14 +44580,14 @@
       <c r="E233" s="6" t="n">
         <v>45842.56371527778</v>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -44771,14 +44771,14 @@
       <c r="E234" s="6" t="n">
         <v>45843.22532407408</v>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -44964,14 +44964,14 @@
       <c r="E235" s="6" t="n">
         <v>45841.81690972222</v>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -45155,14 +45155,14 @@
       <c r="E236" s="6" t="n">
         <v>45842.79640046296</v>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -45346,14 +45346,14 @@
       <c r="E237" s="6" t="n">
         <v>45842.53890046296</v>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -45537,14 +45537,14 @@
       <c r="E238" s="6" t="n">
         <v>45842.53945601852</v>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -45728,14 +45728,14 @@
       <c r="E239" s="6" t="n">
         <v>45842.53950231482</v>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -45919,14 +45919,14 @@
       <c r="E240" s="6" t="n">
         <v>45842.54289351852</v>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -46110,14 +46110,14 @@
       <c r="E241" s="6" t="n">
         <v>45842.5430324074</v>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -46301,14 +46301,14 @@
       <c r="E242" s="6" t="n">
         <v>45842.93369212963</v>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -46490,14 +46490,14 @@
       <c r="E243" s="6" t="n">
         <v>45842.71942129629</v>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -46679,14 +46679,14 @@
       <c r="E244" s="6" t="n">
         <v>45842.48190972222</v>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -46870,14 +46870,14 @@
       <c r="E245" s="6" t="n">
         <v>45843.24831018518</v>
       </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G245" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -47061,14 +47061,14 @@
       <c r="E246" s="6" t="n">
         <v>45842.51211805556</v>
       </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -47252,14 +47252,14 @@
       <c r="E247" s="6" t="n">
         <v>45843.24150462963</v>
       </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G247" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -47443,14 +47443,14 @@
       <c r="E248" s="6" t="n">
         <v>45843.24150462963</v>
       </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G248" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -47634,14 +47634,14 @@
       <c r="E249" s="6" t="n">
         <v>45842.93237268519</v>
       </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G249" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -47823,14 +47823,14 @@
       <c r="E250" s="6" t="n">
         <v>45841.68376157407</v>
       </c>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G250" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -48012,14 +48012,14 @@
       <c r="E251" s="6" t="n">
         <v>45843.23429398148</v>
       </c>
-      <c r="F251" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G251" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -48203,14 +48203,14 @@
       <c r="E252" s="6" t="n">
         <v>45842.85024305555</v>
       </c>
-      <c r="F252" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G252" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -48394,14 +48394,14 @@
       <c r="E253" s="6" t="n">
         <v>45842.51331018518</v>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G253" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -48585,14 +48585,14 @@
       <c r="E254" s="6" t="n">
         <v>45842.68862268519</v>
       </c>
-      <c r="F254" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G254" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -48776,14 +48776,14 @@
       <c r="E255" s="6" t="n">
         <v>45842.84894675926</v>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -48967,14 +48967,14 @@
       <c r="E256" s="6" t="n">
         <v>45842.75037037037</v>
       </c>
-      <c r="F256" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G256" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -49158,14 +49158,14 @@
       <c r="E257" s="6" t="n">
         <v>45842.52549768519</v>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G257" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F257" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G257" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -49349,14 +49349,14 @@
       <c r="E258" s="6" t="n">
         <v>45842.47329861111</v>
       </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G258" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
@@ -49540,14 +49540,14 @@
       <c r="E259" s="6" t="n">
         <v>45843.211875</v>
       </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G259" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
@@ -49731,14 +49731,14 @@
       <c r="E260" s="6" t="n">
         <v>45843.20966435185</v>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -49922,14 +49922,14 @@
       <c r="E261" s="6" t="n">
         <v>45842.75457175926</v>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -50111,14 +50111,14 @@
       <c r="E262" s="6" t="n">
         <v>45842.75458333334</v>
       </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -50300,14 +50300,14 @@
       <c r="E263" s="6" t="n">
         <v>45842.84893518518</v>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -50491,14 +50491,14 @@
       <c r="E264" s="6" t="n">
         <v>45842.9441087963</v>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -50680,14 +50680,14 @@
       <c r="E265" s="6" t="n">
         <v>45842.9441087963</v>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -50871,14 +50871,14 @@
       <c r="E266" s="6" t="n">
         <v>45842.93894675926</v>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
@@ -51060,14 +51060,14 @@
       <c r="E267" s="6" t="n">
         <v>45842.67949074074</v>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -51253,14 +51253,14 @@
       <c r="E268" s="6" t="n">
         <v>45844.75393518519</v>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -51444,14 +51444,14 @@
       <c r="E269" s="6" t="n">
         <v>45844.75393518519</v>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -51635,14 +51635,14 @@
       <c r="E270" s="6" t="n">
         <v>45844.75375</v>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -51826,14 +51826,14 @@
       <c r="E271" s="6" t="n">
         <v>45843.5037962963</v>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -52017,14 +52017,14 @@
       <c r="E272" s="6" t="n">
         <v>45843.92788194444</v>
       </c>
-      <c r="F272" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F272" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
+        </is>
+      </c>
+      <c r="G272" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
@@ -52208,14 +52208,14 @@
       <c r="E273" s="6" t="n">
         <v>45844.04221064815</v>
       </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G273" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>16 a 23 dias</t>
+        </is>
+      </c>
+      <c r="G273" s="7" t="inlineStr">
+        <is>
+          <t>24 a 31 dias</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
